--- a/exports/casos-solicitud.xlsx
+++ b/exports/casos-solicitud.xlsx
@@ -440,7 +440,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AT7"/>
+  <dimension ref="A1:AT8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1700,6 +1700,135 @@
         </is>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>6a352821d3bbe1837</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2026-06-19 11:25:00</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>ENV-AIR-1-2026</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>2026-2</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Carmen Elisa Mejía Torres</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>1023456789</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Cra 48 # 32-15, apto 501</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>3109876543</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Las Flores</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Personal</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>AIRE</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>Afectaciones por ruido</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Verificación</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>Remisión</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>Restaurante El Fogón de Envigado</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>9015567890</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>6045123456</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr"/>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Zona Centro</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Desde hace 3 semanas el restaurante reproduce música a alto volumen después de las 10 p.m., afectando el descanso de los residentes del conjunto. Se han presentado quejas verbales sin respuesta.</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>Se informó a la peticionaria que se programará visita de verificación y se aplicará el protocolo de ruido ambiental.</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>Juan Carlos Sanchez</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>Edwin radica</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>patrullero 1</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/exports/casos-solicitud.xlsx
+++ b/exports/casos-solicitud.xlsx
@@ -1318,6 +1318,11 @@
           <t>Edwin radica</t>
         </is>
       </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>patrullero 2</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -2143,7 +2148,6 @@
           <t>establecimiento</t>
         </is>
       </c>
-      <c r="AT9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
